--- a/ecosysem/kinetics/Excels/MM_AtmMicr.xlsx
+++ b/ecosysem/kinetics/Excels/MM_AtmMicr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartinez\Documents\GitHub\EcoSysEM\ecosysem\kinetics\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6E0409-5D03-4692-8CDB-AAE6388E8EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1C3218-B762-4215-9872-5FFF7CB7F6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -430,8 +430,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -538,8 +538,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
